--- a/artifacts/input/maersk_jobs.xlsx
+++ b/artifacts/input/maersk_jobs.xlsx
@@ -490,7 +490,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F223"/>
+  <dimension ref="A1:F254"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40.85546875" customWidth="1" min="1" max="1"/>
@@ -6970,6 +6970,781 @@
         <v>224</v>
       </c>
     </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>Itajai (Santa Catarina), Brazil</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>Mariel, Cuba</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>CUMAR</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>Mariel, Cuba</t>
+        </is>
+      </c>
+      <c r="F224" t="n">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>Salvador (Bahia), Brazil</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>Mariel, Cuba</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>CUMAR</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>Mariel, Cuba</t>
+        </is>
+      </c>
+      <c r="F225" t="n">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>Santos (Sao Paulo), Brazil</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>Mariel, Cuba</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>CUMAR</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>Mariel, Cuba</t>
+        </is>
+      </c>
+      <c r="F226" t="n">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>Itajai (Santa Catarina), Brazil</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>Manzanillo (Colima), Mexico</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>PAMIT</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>Manzanillo (Colima), Mexico</t>
+        </is>
+      </c>
+      <c r="F227" t="n">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>Salvador (Bahia), Brazil</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>Manzanillo (Colima), Mexico</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>PAMIT</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>Manzanillo (Colima), Mexico</t>
+        </is>
+      </c>
+      <c r="F228" t="n">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>Santos (Sao Paulo), Brazil</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>Manzanillo (Colima), Mexico</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>PAMIT</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>Manzanillo (Colima), Mexico</t>
+        </is>
+      </c>
+      <c r="F229" t="n">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>Itajai (Santa Catarina), Brazil</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>Grand Cayman, Cayman Islands</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>KYGCM</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>Grand Cayman, Cayman Islands</t>
+        </is>
+      </c>
+      <c r="F230" t="n">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>Salvador (Bahia), Brazil</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>Grand Cayman, Cayman Islands</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>KYGCM</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>Grand Cayman, Cayman Islands</t>
+        </is>
+      </c>
+      <c r="F231" t="n">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>Santos (Sao Paulo), Brazil</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>Grand Cayman, Cayman Islands</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>KYGCM</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>Grand Cayman, Cayman Islands</t>
+        </is>
+      </c>
+      <c r="F232" t="n">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>Suape (Pernambuco), Brazil</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>Basseterre, St Kitts-Nevis</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>KNBAS</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>Basseterre, St Kitts-Nevis</t>
+        </is>
+      </c>
+      <c r="F233" t="n">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>Suape (Pernambuco), Brazil</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>Bridgetown, Barbados</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>BBBGI</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>Bridgetown, Barbados</t>
+        </is>
+      </c>
+      <c r="F234" t="n">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>Suape (Pernambuco), Brazil</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>Campden Park, Saint Vincent and the Grenadines</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>VCCRP</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>Campden Park, Saint Vincent and the Grenadines</t>
+        </is>
+      </c>
+      <c r="F235" t="n">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>Suape (Pernambuco), Brazil</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>Caucedo, Dominican Republic</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>DOCAU</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>Caucedo, Dominican Republic</t>
+        </is>
+      </c>
+      <c r="F236" t="n">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>Suape (Pernambuco), Brazil</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>Cristobal, Panama</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>PACTB</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>Cristobal, Panama</t>
+        </is>
+      </c>
+      <c r="F237" t="n">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>Suape (Pernambuco), Brazil</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>Freeport, Bahamas</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>BSFPO</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>Freeport, Bahamas</t>
+        </is>
+      </c>
+      <c r="F238" t="n">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>Suape (Pernambuco), Brazil</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>Georgetown, Guyana</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>AUGEE</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>Georgetown, Guyana</t>
+        </is>
+      </c>
+      <c r="F239" t="n">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>Suape (Pernambuco), Brazil</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>Kingston, Jamaica</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>JMKIN</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>Kingston, Jamaica</t>
+        </is>
+      </c>
+      <c r="F240" t="n">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>Suape (Pernambuco), Brazil</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>KRALENDIJK, BONAIRE</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>BQKRA</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>KRALENDIJK, BONAIRE</t>
+        </is>
+      </c>
+      <c r="F241" t="n">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>Suape (Pernambuco), Brazil</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>Nassau, Bahamas</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>BSNAS</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>Nassau, Bahamas</t>
+        </is>
+      </c>
+      <c r="F242" t="n">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>Suape (Pernambuco), Brazil</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>Oranjestad, Aruba</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>AWORJ</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>Oranjestad, Aruba</t>
+        </is>
+      </c>
+      <c r="F243" t="n">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>Suape (Pernambuco), Brazil</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>Paramaribo, Suriname</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>SRPBM</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>Paramaribo, Suriname</t>
+        </is>
+      </c>
+      <c r="F244" t="n">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>Suape (Pernambuco), Brazil</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>Port of Spain-Trinidad, Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>TTPOS</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>Port of Spain-Trinidad, Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="F245" t="n">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>Suape (Pernambuco), Brazil</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>Road Town, Virgin Islands (Br.)</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>VGRAD</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>Road Town, Virgin Islands (Br.)</t>
+        </is>
+      </c>
+      <c r="F246" t="n">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>Suape (Pernambuco), Brazil</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>Roseau, Dominica</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>DMRSU</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>Roseau, Dominica</t>
+        </is>
+      </c>
+      <c r="F247" t="n">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>Suape (Pernambuco), Brazil</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>Saint George, Grenada</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>GDSTG</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>Saint George, Grenada</t>
+        </is>
+      </c>
+      <c r="F248" t="n">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>Suape (Pernambuco), Brazil</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>San Juan, Puerto Rico</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>PRSJU</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>San Juan, Puerto Rico</t>
+        </is>
+      </c>
+      <c r="F249" t="n">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>Suape (Pernambuco), Brazil</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>St Johns, Antigua and Barbuda</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>AGSJO</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>St Johns, Antigua and Barbuda</t>
+        </is>
+      </c>
+      <c r="F250" t="n">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>Suape (Pernambuco), Brazil</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>Willemstad, Curacao</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>ANWIL</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>Willemstad, Curacao</t>
+        </is>
+      </c>
+      <c r="F251" t="n">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>Suape (Pernambuco), Brazil</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>Mariel, Cuba</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>CUMAR</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>Mariel, Cuba</t>
+        </is>
+      </c>
+      <c r="F252" t="n">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>Suape (Pernambuco), Brazil</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>Manzanillo (Colima), Mexico</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>PAMIT</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>Manzanillo (Colima), Mexico</t>
+        </is>
+      </c>
+      <c r="F253" t="n">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>Suape (Pernambuco), Brazil</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>Grand Cayman, Cayman Islands</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>KYGCM</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>Grand Cayman, Cayman Islands</t>
+        </is>
+      </c>
+      <c r="F254" t="n">
+        <v>255</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F223">
     <sortState ref="A2:F223">

--- a/artifacts/input/maersk_jobs.xlsx
+++ b/artifacts/input/maersk_jobs.xlsx
@@ -490,7 +490,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F254"/>
+  <dimension ref="A1:I261"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40.85546875" customWidth="1" min="1" max="1"/>
@@ -531,6 +531,21 @@
           <t>indexador</t>
         </is>
       </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>porto de compara??o</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>combina??o</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>PORTO DE DESTINO.1</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -7743,6 +7758,181 @@
       </c>
       <c r="F254" t="n">
         <v>255</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>Rio de Janeiro (Rio de Janeiro), Brazil</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>Santo Tomas de Castilla, Guatemala</t>
+        </is>
+      </c>
+      <c r="F255" t="n">
+        <v>257</v>
+      </c>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>GTSTC</t>
+        </is>
+      </c>
+      <c r="I255" t="inlineStr">
+        <is>
+          <t>Santo Tomas de Castilla, Guatemala</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>Vitoria (Espirito Santo), Brazil</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>Altamira (Tamaulipas), Mexico</t>
+        </is>
+      </c>
+      <c r="F256" t="n">
+        <v>258</v>
+      </c>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>MXATM</t>
+        </is>
+      </c>
+      <c r="I256" t="inlineStr">
+        <is>
+          <t>Altamira (Tamaulipas), Mexico</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>Vitoria (Espirito Santo), Brazil</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>Veracruz (Veracruz Llave), Mexico</t>
+        </is>
+      </c>
+      <c r="F257" t="n">
+        <v>259</v>
+      </c>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>MXVCR</t>
+        </is>
+      </c>
+      <c r="I257" t="inlineStr">
+        <is>
+          <t>Veracruz (Veracruz Llave), Mexico</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>Rio de Janeiro (Rio de Janeiro), Brazil</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>Manzanillo, Panama</t>
+        </is>
+      </c>
+      <c r="F258" t="n">
+        <v>265</v>
+      </c>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t>PAMIT</t>
+        </is>
+      </c>
+      <c r="I258" t="inlineStr">
+        <is>
+          <t>Manzanillo, Panama</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>Rio de Janeiro (Rio de Janeiro), Brazil</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>Caucedo, Dominican Republic</t>
+        </is>
+      </c>
+      <c r="F259" t="n">
+        <v>266</v>
+      </c>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t>DOCAU</t>
+        </is>
+      </c>
+      <c r="I259" t="inlineStr">
+        <is>
+          <t>Caucedo, Dominican Republic</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>Rio de Janeiro (Rio de Janeiro), Brazil</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>San Juan, Puerto Rico</t>
+        </is>
+      </c>
+      <c r="F260" t="n">
+        <v>267</v>
+      </c>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>PRSJU</t>
+        </is>
+      </c>
+      <c r="I260" t="inlineStr">
+        <is>
+          <t>San Juan, Puerto Rico</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>Rio de Janeiro (Rio de Janeiro), Brazil</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>Cartagena (Bolivar), Colombia</t>
+        </is>
+      </c>
+      <c r="F261" t="n">
+        <v>268</v>
+      </c>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>COCTG</t>
+        </is>
+      </c>
+      <c r="I261" t="inlineStr">
+        <is>
+          <t>Cartagena (Bolivar), Colombia</t>
+        </is>
       </c>
     </row>
   </sheetData>
